--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276069</v>
+        <v>120276068</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777617</v>
+        <v>777581</v>
       </c>
       <c r="R2" t="n">
-        <v>7299807</v>
+        <v>7299777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276065</v>
+        <v>120276073</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777859</v>
+        <v>777708</v>
       </c>
       <c r="R3" t="n">
-        <v>7299767</v>
+        <v>7299857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276073</v>
+        <v>120276076</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777708</v>
+        <v>777733</v>
       </c>
       <c r="R4" t="n">
-        <v>7299857</v>
+        <v>7299878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>120276075</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276076</v>
+        <v>120276072</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777733</v>
+        <v>777699</v>
       </c>
       <c r="R6" t="n">
-        <v>7299878</v>
+        <v>7299851</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120276070</v>
+        <v>120276066</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777630</v>
+        <v>777536</v>
       </c>
       <c r="R7" t="n">
-        <v>7299810</v>
+        <v>7299705</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,17 +1284,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120276072</v>
+        <v>120276070</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777699</v>
+        <v>777630</v>
       </c>
       <c r="R8" t="n">
-        <v>7299851</v>
+        <v>7299810</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120276068</v>
+        <v>120276065</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777581</v>
+        <v>777859</v>
       </c>
       <c r="R9" t="n">
-        <v>7299777</v>
+        <v>7299767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1488,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1494,7 +1498,7 @@
         <v>120276071</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120276066</v>
+        <v>120276069</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,42 +1609,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777536</v>
+        <v>777617</v>
       </c>
       <c r="R11" t="n">
-        <v>7299705</v>
+        <v>7299807</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276068</v>
+        <v>120276071</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777581</v>
+        <v>777669</v>
       </c>
       <c r="R2" t="n">
-        <v>7299777</v>
+        <v>7299857</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276073</v>
+        <v>120276065</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777708</v>
+        <v>777859</v>
       </c>
       <c r="R3" t="n">
-        <v>7299857</v>
+        <v>7299767</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,14 +872,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276076</v>
+        <v>120276070</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777733</v>
+        <v>777630</v>
       </c>
       <c r="R4" t="n">
-        <v>7299878</v>
+        <v>7299810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276075</v>
+        <v>120276072</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777721</v>
+        <v>777699</v>
       </c>
       <c r="R5" t="n">
-        <v>7299859</v>
+        <v>7299851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276072</v>
+        <v>120276068</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777699</v>
+        <v>777581</v>
       </c>
       <c r="R6" t="n">
-        <v>7299851</v>
+        <v>7299777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120276066</v>
+        <v>120276069</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,42 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777536</v>
+        <v>777617</v>
       </c>
       <c r="R7" t="n">
-        <v>7299705</v>
+        <v>7299807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,14 +1280,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120276070</v>
+        <v>120276075</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1331,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777630</v>
+        <v>777721</v>
       </c>
       <c r="R8" t="n">
-        <v>7299810</v>
+        <v>7299859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120276065</v>
+        <v>120276066</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1427,16 +1423,20 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777859</v>
+        <v>777536</v>
       </c>
       <c r="R9" t="n">
-        <v>7299767</v>
+        <v>7299705</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120276071</v>
+        <v>120276073</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777669</v>
+        <v>777708</v>
       </c>
       <c r="R10" t="n">
         <v>7299857</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120276069</v>
+        <v>120276076</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777617</v>
+        <v>777733</v>
       </c>
       <c r="R11" t="n">
-        <v>7299807</v>
+        <v>7299878</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,6 +1696,2761 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120400078</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>777481</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7299820</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120400097</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>777509</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7299783</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120400094</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>777533</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7299712</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120400077</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>777488</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7299834</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120400095</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>777538</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7299701</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120400079</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>777510</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7299803</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120400083</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>777513</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7299751</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120400073</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>777546</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7299709</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120400068</v>
+      </c>
+      <c r="B20" t="n">
+        <v>77926</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>777515</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7299746</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120400066</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90742</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>777519</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7299799</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120400090</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>777515</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7299848</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120400081</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>777538</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7299782</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120400098</v>
+      </c>
+      <c r="B24" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>777548</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7299735</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120400096</v>
+      </c>
+      <c r="B25" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>777470</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7299820</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120400088</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>777536</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7299724</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120400100</v>
+      </c>
+      <c r="B27" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>777528</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7299721</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120400076</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>777566</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7299811</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120400084</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>777510</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7299742</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120400092</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>777528</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7299779</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120400085</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>777542</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7299749</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120400080</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>777509</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7299785</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120400075</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>777572</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7299804</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120400082</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>777520</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7299766</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120400089</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>777544</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7299841</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120400067</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>777506</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7299869</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120400086</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>777544</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7299734</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120400074</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>777555</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7299761</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276071</v>
+        <v>120276069</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777669</v>
+        <v>777617</v>
       </c>
       <c r="R2" t="n">
-        <v>7299857</v>
+        <v>7299807</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276065</v>
+        <v>120276071</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777859</v>
+        <v>777669</v>
       </c>
       <c r="R3" t="n">
-        <v>7299767</v>
+        <v>7299857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,14 +872,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276070</v>
+        <v>120276073</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777630</v>
+        <v>777708</v>
       </c>
       <c r="R4" t="n">
-        <v>7299810</v>
+        <v>7299857</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276072</v>
+        <v>120276066</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777699</v>
+        <v>777536</v>
       </c>
       <c r="R5" t="n">
-        <v>7299851</v>
+        <v>7299705</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,14 +1080,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276068</v>
+        <v>120276075</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777581</v>
+        <v>777721</v>
       </c>
       <c r="R6" t="n">
-        <v>7299777</v>
+        <v>7299859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120276069</v>
+        <v>120276068</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777617</v>
+        <v>777581</v>
       </c>
       <c r="R7" t="n">
-        <v>7299807</v>
+        <v>7299777</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120276075</v>
+        <v>120276065</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1303,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777721</v>
+        <v>777859</v>
       </c>
       <c r="R8" t="n">
-        <v>7299859</v>
+        <v>7299767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,17 +1386,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120276066</v>
+        <v>120276070</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,42 +1405,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777536</v>
+        <v>777630</v>
       </c>
       <c r="R9" t="n">
-        <v>7299705</v>
+        <v>7299810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,14 +1488,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120276073</v>
+        <v>120276072</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777708</v>
+        <v>777699</v>
       </c>
       <c r="R10" t="n">
-        <v>7299857</v>
+        <v>7299851</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120400078</v>
+        <v>120400084</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777481</v>
+        <v>777510</v>
       </c>
       <c r="R12" t="n">
-        <v>7299820</v>
+        <v>7299742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400097</v>
+        <v>120400095</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777509</v>
+        <v>777538</v>
       </c>
       <c r="R13" t="n">
-        <v>7299783</v>
+        <v>7299701</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400094</v>
+        <v>120400074</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777533</v>
+        <v>777555</v>
       </c>
       <c r="R14" t="n">
-        <v>7299712</v>
+        <v>7299761</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120400077</v>
+        <v>120400078</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777488</v>
+        <v>777481</v>
       </c>
       <c r="R15" t="n">
-        <v>7299834</v>
+        <v>7299820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120400095</v>
+        <v>120400100</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777538</v>
+        <v>777528</v>
       </c>
       <c r="R16" t="n">
-        <v>7299701</v>
+        <v>7299721</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2191,6 +2191,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2209,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400079</v>
+        <v>120400077</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2249,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777510</v>
+        <v>777488</v>
       </c>
       <c r="R17" t="n">
-        <v>7299803</v>
+        <v>7299834</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120400083</v>
+        <v>120400096</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777513</v>
+        <v>777470</v>
       </c>
       <c r="R18" t="n">
-        <v>7299751</v>
+        <v>7299820</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400073</v>
+        <v>120400097</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777546</v>
+        <v>777509</v>
       </c>
       <c r="R19" t="n">
-        <v>7299709</v>
+        <v>7299783</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120400068</v>
+        <v>120400083</v>
       </c>
       <c r="B20" t="n">
-        <v>77926</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777515</v>
+        <v>777513</v>
       </c>
       <c r="R20" t="n">
-        <v>7299746</v>
+        <v>7299751</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120400081</v>
+        <v>120400067</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2861,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777538</v>
+        <v>777506</v>
       </c>
       <c r="R23" t="n">
-        <v>7299782</v>
+        <v>7299869</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120400098</v>
+        <v>120400085</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777548</v>
+        <v>777542</v>
       </c>
       <c r="R24" t="n">
-        <v>7299735</v>
+        <v>7299749</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400096</v>
+        <v>120400080</v>
       </c>
       <c r="B25" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3065,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777470</v>
+        <v>777509</v>
       </c>
       <c r="R25" t="n">
-        <v>7299820</v>
+        <v>7299785</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,7 +3128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120400088</v>
+        <v>120400073</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3167,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777536</v>
+        <v>777546</v>
       </c>
       <c r="R26" t="n">
-        <v>7299724</v>
+        <v>7299709</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120400100</v>
+        <v>120400092</v>
       </c>
       <c r="B27" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3245,21 +3246,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3272,7 +3273,7 @@
         <v>777528</v>
       </c>
       <c r="R27" t="n">
-        <v>7299721</v>
+        <v>7299779</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3313,7 +3314,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400076</v>
+        <v>120400086</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777566</v>
+        <v>777544</v>
       </c>
       <c r="R28" t="n">
-        <v>7299811</v>
+        <v>7299734</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400084</v>
+        <v>120400082</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777510</v>
+        <v>777520</v>
       </c>
       <c r="R29" t="n">
-        <v>7299742</v>
+        <v>7299766</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400092</v>
+        <v>120400081</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,25 +3548,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777528</v>
+        <v>777538</v>
       </c>
       <c r="R30" t="n">
-        <v>7299779</v>
+        <v>7299782</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120400085</v>
+        <v>120400079</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777542</v>
+        <v>777510</v>
       </c>
       <c r="R31" t="n">
-        <v>7299749</v>
+        <v>7299803</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120400080</v>
+        <v>120400098</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777509</v>
+        <v>777548</v>
       </c>
       <c r="R32" t="n">
-        <v>7299785</v>
+        <v>7299735</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120400082</v>
+        <v>120400089</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777520</v>
+        <v>777544</v>
       </c>
       <c r="R34" t="n">
-        <v>7299766</v>
+        <v>7299841</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120400089</v>
+        <v>120400068</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>77926</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777544</v>
+        <v>777515</v>
       </c>
       <c r="R35" t="n">
-        <v>7299841</v>
+        <v>7299746</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400067</v>
+        <v>120400088</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777506</v>
+        <v>777536</v>
       </c>
       <c r="R36" t="n">
-        <v>7299869</v>
+        <v>7299724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120400086</v>
+        <v>120400094</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4262,25 +4262,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777544</v>
+        <v>777533</v>
       </c>
       <c r="R37" t="n">
-        <v>7299734</v>
+        <v>7299712</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400074</v>
+        <v>120400076</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777555</v>
+        <v>777566</v>
       </c>
       <c r="R38" t="n">
-        <v>7299761</v>
+        <v>7299811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,6 +4451,2556 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120447927</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>777807</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7299862</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120447932</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>777654</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7299823</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120447924</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>777757</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7299786</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120447940</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>777720</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7299943</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120447923</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>777708</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7299768</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120447943</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>777591</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7299752</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120447933</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>777676</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7299816</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120447945</v>
+      </c>
+      <c r="B46" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>777657</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7299864</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120447936</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>777575</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7299706</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120447928</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>777734</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7299914</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120447942</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>777618</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7299777</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120447930</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>777677</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7299863</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120447946</v>
+      </c>
+      <c r="B51" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>777590</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7299753</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120447917</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>777575</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7299735</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120447947</v>
+      </c>
+      <c r="B53" t="n">
+        <v>77926</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>777767</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7299946</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120447915</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>777762</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7299968</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120447926</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>777821</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7299833</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120447929</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>777717</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7299901</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120447931</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>777660</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7299834</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120447916</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90084</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>777801</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7299907</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120447934</v>
+      </c>
+      <c r="B59" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>777607</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7299771</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120447937</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>777569</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7299706</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120447914</v>
+      </c>
+      <c r="B61" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>777574</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7299687</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120447941</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>777712</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7299892</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120447935</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>777588</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7299750</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276075</v>
+        <v>120276065</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777721</v>
+        <v>777859</v>
       </c>
       <c r="R6" t="n">
-        <v>7299859</v>
+        <v>7299767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,14 +1182,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120276068</v>
+        <v>120276075</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777581</v>
+        <v>777721</v>
       </c>
       <c r="R7" t="n">
-        <v>7299777</v>
+        <v>7299859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120276065</v>
+        <v>120276068</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,25 +1303,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777859</v>
+        <v>777581</v>
       </c>
       <c r="R8" t="n">
-        <v>7299767</v>
+        <v>7299777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276071</v>
+        <v>120276070</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777669</v>
+        <v>777630</v>
       </c>
       <c r="R3" t="n">
-        <v>7299857</v>
+        <v>7299810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276073</v>
+        <v>120276065</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777708</v>
+        <v>777859</v>
       </c>
       <c r="R4" t="n">
-        <v>7299857</v>
+        <v>7299767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276066</v>
+        <v>120276071</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,42 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777536</v>
+        <v>777669</v>
       </c>
       <c r="R5" t="n">
-        <v>7299705</v>
+        <v>7299857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276065</v>
+        <v>120276076</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777859</v>
+        <v>777733</v>
       </c>
       <c r="R6" t="n">
-        <v>7299767</v>
+        <v>7299878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,14 +1178,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120276075</v>
+        <v>120276072</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1229,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777721</v>
+        <v>777699</v>
       </c>
       <c r="R7" t="n">
-        <v>7299859</v>
+        <v>7299851</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1393,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120276070</v>
+        <v>120276075</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1433,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777630</v>
+        <v>777721</v>
       </c>
       <c r="R9" t="n">
-        <v>7299810</v>
+        <v>7299859</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120276072</v>
+        <v>120276073</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1535,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777699</v>
+        <v>777708</v>
       </c>
       <c r="R10" t="n">
-        <v>7299851</v>
+        <v>7299857</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120276076</v>
+        <v>120276066</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,38 +1605,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777733</v>
+        <v>777536</v>
       </c>
       <c r="R11" t="n">
-        <v>7299878</v>
+        <v>7299705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,17 +1692,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120400084</v>
+        <v>120400066</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>90742</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,25 +1711,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777510</v>
+        <v>777519</v>
       </c>
       <c r="R12" t="n">
-        <v>7299742</v>
+        <v>7299799</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400095</v>
+        <v>120400092</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777538</v>
+        <v>777528</v>
       </c>
       <c r="R13" t="n">
-        <v>7299701</v>
+        <v>7299779</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400074</v>
+        <v>120400078</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777555</v>
+        <v>777481</v>
       </c>
       <c r="R14" t="n">
-        <v>7299761</v>
+        <v>7299820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120400078</v>
+        <v>120400073</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777481</v>
+        <v>777546</v>
       </c>
       <c r="R15" t="n">
-        <v>7299820</v>
+        <v>7299709</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120400100</v>
+        <v>120400088</v>
       </c>
       <c r="B16" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777528</v>
+        <v>777536</v>
       </c>
       <c r="R16" t="n">
-        <v>7299721</v>
+        <v>7299724</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2191,7 +2191,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2210,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400077</v>
+        <v>120400096</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2221,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777488</v>
+        <v>777470</v>
       </c>
       <c r="R17" t="n">
-        <v>7299834</v>
+        <v>7299820</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2311,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120400096</v>
+        <v>120400086</v>
       </c>
       <c r="B18" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2323,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777470</v>
+        <v>777544</v>
       </c>
       <c r="R18" t="n">
-        <v>7299820</v>
+        <v>7299734</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2413,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400097</v>
+        <v>120400081</v>
       </c>
       <c r="B19" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2425,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777509</v>
+        <v>777538</v>
       </c>
       <c r="R19" t="n">
-        <v>7299783</v>
+        <v>7299782</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2515,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120400083</v>
+        <v>120400098</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2527,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777513</v>
+        <v>777548</v>
       </c>
       <c r="R20" t="n">
-        <v>7299751</v>
+        <v>7299735</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2617,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120400066</v>
+        <v>120400068</v>
       </c>
       <c r="B21" t="n">
-        <v>90742</v>
+        <v>77926</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2633,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777519</v>
+        <v>777515</v>
       </c>
       <c r="R21" t="n">
-        <v>7299799</v>
+        <v>7299746</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120400090</v>
+        <v>120400080</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2731,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777515</v>
+        <v>777509</v>
       </c>
       <c r="R22" t="n">
-        <v>7299848</v>
+        <v>7299785</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120400067</v>
+        <v>120400076</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2833,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777506</v>
+        <v>777566</v>
       </c>
       <c r="R23" t="n">
-        <v>7299869</v>
+        <v>7299811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120400085</v>
+        <v>120400100</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2935,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777542</v>
+        <v>777528</v>
       </c>
       <c r="R24" t="n">
-        <v>7299749</v>
+        <v>7299721</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3008,6 +3007,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400080</v>
+        <v>120400097</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
         <v>777509</v>
       </c>
       <c r="R25" t="n">
-        <v>7299785</v>
+        <v>7299783</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120400073</v>
+        <v>120400094</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777546</v>
+        <v>777533</v>
       </c>
       <c r="R26" t="n">
-        <v>7299709</v>
+        <v>7299712</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120400092</v>
+        <v>120400084</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777528</v>
+        <v>777510</v>
       </c>
       <c r="R27" t="n">
-        <v>7299779</v>
+        <v>7299742</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400086</v>
+        <v>120400075</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777544</v>
+        <v>777572</v>
       </c>
       <c r="R28" t="n">
-        <v>7299734</v>
+        <v>7299804</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400082</v>
+        <v>120400089</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777520</v>
+        <v>777544</v>
       </c>
       <c r="R29" t="n">
-        <v>7299766</v>
+        <v>7299841</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400081</v>
+        <v>120400085</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777538</v>
+        <v>777542</v>
       </c>
       <c r="R30" t="n">
-        <v>7299782</v>
+        <v>7299749</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120400079</v>
+        <v>120400074</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777510</v>
+        <v>777555</v>
       </c>
       <c r="R31" t="n">
-        <v>7299803</v>
+        <v>7299761</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120400098</v>
+        <v>120400083</v>
       </c>
       <c r="B32" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777548</v>
+        <v>777513</v>
       </c>
       <c r="R32" t="n">
-        <v>7299735</v>
+        <v>7299751</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120400075</v>
+        <v>120400079</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777572</v>
+        <v>777510</v>
       </c>
       <c r="R33" t="n">
-        <v>7299804</v>
+        <v>7299803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120400089</v>
+        <v>120400090</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777544</v>
+        <v>777515</v>
       </c>
       <c r="R34" t="n">
-        <v>7299841</v>
+        <v>7299848</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120400068</v>
+        <v>120400082</v>
       </c>
       <c r="B35" t="n">
-        <v>77926</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777515</v>
+        <v>777520</v>
       </c>
       <c r="R35" t="n">
-        <v>7299746</v>
+        <v>7299766</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400088</v>
+        <v>120400077</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777536</v>
+        <v>777488</v>
       </c>
       <c r="R36" t="n">
-        <v>7299724</v>
+        <v>7299834</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120400094</v>
+        <v>120400067</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777533</v>
+        <v>777506</v>
       </c>
       <c r="R37" t="n">
-        <v>7299712</v>
+        <v>7299869</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400076</v>
+        <v>120400095</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4364,25 +4364,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777566</v>
+        <v>777538</v>
       </c>
       <c r="R38" t="n">
-        <v>7299811</v>
+        <v>7299701</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120447927</v>
+        <v>120447945</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4466,25 +4466,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777807</v>
+        <v>777657</v>
       </c>
       <c r="R39" t="n">
-        <v>7299862</v>
+        <v>7299864</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120447932</v>
+        <v>120447934</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777654</v>
+        <v>777607</v>
       </c>
       <c r="R40" t="n">
-        <v>7299823</v>
+        <v>7299771</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120447924</v>
+        <v>120447942</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777757</v>
+        <v>777618</v>
       </c>
       <c r="R41" t="n">
-        <v>7299786</v>
+        <v>7299777</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120447940</v>
+        <v>120447916</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>90084</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4772,25 +4772,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777720</v>
+        <v>777801</v>
       </c>
       <c r="R42" t="n">
-        <v>7299943</v>
+        <v>7299907</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120447923</v>
+        <v>120447930</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777708</v>
+        <v>777677</v>
       </c>
       <c r="R43" t="n">
-        <v>7299768</v>
+        <v>7299863</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120447943</v>
+        <v>120447923</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4976,25 +4976,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777591</v>
+        <v>777708</v>
       </c>
       <c r="R44" t="n">
-        <v>7299752</v>
+        <v>7299768</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120447933</v>
+        <v>120447926</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777676</v>
+        <v>777821</v>
       </c>
       <c r="R45" t="n">
-        <v>7299816</v>
+        <v>7299833</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5168,7 +5168,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120447945</v>
+        <v>120447946</v>
       </c>
       <c r="B46" t="n">
         <v>82321</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777657</v>
+        <v>777590</v>
       </c>
       <c r="R46" t="n">
-        <v>7299864</v>
+        <v>7299753</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120447936</v>
+        <v>120447914</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5282,25 +5282,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777575</v>
+        <v>777574</v>
       </c>
       <c r="R47" t="n">
-        <v>7299706</v>
+        <v>7299687</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5372,10 +5372,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120447928</v>
+        <v>120447941</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5384,25 +5384,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777734</v>
+        <v>777712</v>
       </c>
       <c r="R48" t="n">
-        <v>7299914</v>
+        <v>7299892</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5474,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120447942</v>
+        <v>120447927</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5486,25 +5486,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777618</v>
+        <v>777807</v>
       </c>
       <c r="R49" t="n">
-        <v>7299777</v>
+        <v>7299862</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120447930</v>
+        <v>120447947</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5588,25 +5588,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>777677</v>
+        <v>777767</v>
       </c>
       <c r="R50" t="n">
-        <v>7299863</v>
+        <v>7299946</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120447946</v>
+        <v>120447931</v>
       </c>
       <c r="B51" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5690,25 +5690,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>777590</v>
+        <v>777660</v>
       </c>
       <c r="R51" t="n">
-        <v>7299753</v>
+        <v>7299834</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120447917</v>
+        <v>120447932</v>
       </c>
       <c r="B52" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5792,25 +5792,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777575</v>
+        <v>777654</v>
       </c>
       <c r="R52" t="n">
-        <v>7299735</v>
+        <v>7299823</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120447947</v>
+        <v>120447915</v>
       </c>
       <c r="B53" t="n">
-        <v>77926</v>
+        <v>57473</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5898,21 +5898,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777767</v>
+        <v>777762</v>
       </c>
       <c r="R53" t="n">
-        <v>7299946</v>
+        <v>7299968</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,10 +5984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120447915</v>
+        <v>120447935</v>
       </c>
       <c r="B54" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5996,25 +5996,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>777762</v>
+        <v>777588</v>
       </c>
       <c r="R54" t="n">
-        <v>7299968</v>
+        <v>7299750</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120447926</v>
+        <v>120447924</v>
       </c>
       <c r="B55" t="n">
         <v>97930</v>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>777821</v>
+        <v>777757</v>
       </c>
       <c r="R55" t="n">
-        <v>7299833</v>
+        <v>7299786</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6188,7 +6188,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120447929</v>
+        <v>120447928</v>
       </c>
       <c r="B56" t="n">
         <v>97930</v>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>777717</v>
+        <v>777734</v>
       </c>
       <c r="R56" t="n">
-        <v>7299901</v>
+        <v>7299914</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120447931</v>
+        <v>120447929</v>
       </c>
       <c r="B57" t="n">
         <v>97930</v>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>777660</v>
+        <v>777717</v>
       </c>
       <c r="R57" t="n">
-        <v>7299834</v>
+        <v>7299901</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6392,10 +6392,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120447916</v>
+        <v>120447943</v>
       </c>
       <c r="B58" t="n">
-        <v>90084</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6404,25 +6404,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>777801</v>
+        <v>777591</v>
       </c>
       <c r="R58" t="n">
-        <v>7299907</v>
+        <v>7299752</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6494,7 +6494,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120447934</v>
+        <v>120447936</v>
       </c>
       <c r="B59" t="n">
         <v>97930</v>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>777607</v>
+        <v>777575</v>
       </c>
       <c r="R59" t="n">
-        <v>7299771</v>
+        <v>7299706</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120447914</v>
+        <v>120447940</v>
       </c>
       <c r="B61" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6710,25 +6710,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>777574</v>
+        <v>777720</v>
       </c>
       <c r="R61" t="n">
-        <v>7299687</v>
+        <v>7299943</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6800,10 +6800,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120447941</v>
+        <v>120447933</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6812,25 +6812,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>777712</v>
+        <v>777676</v>
       </c>
       <c r="R62" t="n">
-        <v>7299892</v>
+        <v>7299816</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120447935</v>
+        <v>120447917</v>
       </c>
       <c r="B63" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777588</v>
+        <v>777575</v>
       </c>
       <c r="R63" t="n">
-        <v>7299750</v>
+        <v>7299735</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276069</v>
+        <v>120276073</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777617</v>
+        <v>777708</v>
       </c>
       <c r="R2" t="n">
-        <v>7299807</v>
+        <v>7299857</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276070</v>
+        <v>120276068</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777630</v>
+        <v>777581</v>
       </c>
       <c r="R3" t="n">
-        <v>7299810</v>
+        <v>7299777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276065</v>
+        <v>120276070</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777859</v>
+        <v>777630</v>
       </c>
       <c r="R4" t="n">
-        <v>7299767</v>
+        <v>7299810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276076</v>
+        <v>120276069</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777733</v>
+        <v>777617</v>
       </c>
       <c r="R6" t="n">
-        <v>7299878</v>
+        <v>7299807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120276072</v>
+        <v>120276076</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777699</v>
+        <v>777733</v>
       </c>
       <c r="R7" t="n">
-        <v>7299851</v>
+        <v>7299878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120276068</v>
+        <v>120276075</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777581</v>
+        <v>777721</v>
       </c>
       <c r="R8" t="n">
-        <v>7299777</v>
+        <v>7299859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120276075</v>
+        <v>120276065</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777721</v>
+        <v>777859</v>
       </c>
       <c r="R9" t="n">
-        <v>7299859</v>
+        <v>7299767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,14 +1484,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120276073</v>
+        <v>120276072</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777708</v>
+        <v>777699</v>
       </c>
       <c r="R10" t="n">
-        <v>7299857</v>
+        <v>7299851</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400092</v>
+        <v>120400083</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,25 +1813,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777528</v>
+        <v>777513</v>
       </c>
       <c r="R13" t="n">
-        <v>7299779</v>
+        <v>7299751</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400078</v>
+        <v>120400090</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777481</v>
+        <v>777515</v>
       </c>
       <c r="R14" t="n">
-        <v>7299820</v>
+        <v>7299848</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120400073</v>
+        <v>120400067</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,25 +2017,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777546</v>
+        <v>777506</v>
       </c>
       <c r="R15" t="n">
-        <v>7299709</v>
+        <v>7299869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120400088</v>
+        <v>120400068</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777536</v>
+        <v>777515</v>
       </c>
       <c r="R16" t="n">
-        <v>7299724</v>
+        <v>7299746</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400096</v>
+        <v>120400073</v>
       </c>
       <c r="B17" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,25 +2221,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777470</v>
+        <v>777546</v>
       </c>
       <c r="R17" t="n">
-        <v>7299820</v>
+        <v>7299709</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120400086</v>
+        <v>120400075</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777544</v>
+        <v>777572</v>
       </c>
       <c r="R18" t="n">
-        <v>7299734</v>
+        <v>7299804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400081</v>
+        <v>120400074</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777538</v>
+        <v>777555</v>
       </c>
       <c r="R19" t="n">
-        <v>7299782</v>
+        <v>7299761</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120400098</v>
+        <v>120400097</v>
       </c>
       <c r="B20" t="n">
         <v>82321</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777548</v>
+        <v>777509</v>
       </c>
       <c r="R20" t="n">
-        <v>7299735</v>
+        <v>7299783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,10 +2617,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120400068</v>
+        <v>120400096</v>
       </c>
       <c r="B21" t="n">
-        <v>77926</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777515</v>
+        <v>777470</v>
       </c>
       <c r="R21" t="n">
-        <v>7299746</v>
+        <v>7299820</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120400080</v>
+        <v>120400078</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777509</v>
+        <v>777481</v>
       </c>
       <c r="R22" t="n">
-        <v>7299785</v>
+        <v>7299820</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120400076</v>
+        <v>120400098</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,25 +2833,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777566</v>
+        <v>777548</v>
       </c>
       <c r="R23" t="n">
-        <v>7299811</v>
+        <v>7299735</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120400100</v>
+        <v>120400081</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,25 +2935,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777528</v>
+        <v>777538</v>
       </c>
       <c r="R24" t="n">
-        <v>7299721</v>
+        <v>7299782</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3007,7 +3007,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3026,10 +3025,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400097</v>
+        <v>120400082</v>
       </c>
       <c r="B25" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3037,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777509</v>
+        <v>777520</v>
       </c>
       <c r="R25" t="n">
-        <v>7299783</v>
+        <v>7299766</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120400094</v>
+        <v>120400095</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3168,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777533</v>
+        <v>777538</v>
       </c>
       <c r="R26" t="n">
-        <v>7299712</v>
+        <v>7299701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3229,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120400084</v>
+        <v>120400094</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3241,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3269,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777510</v>
+        <v>777533</v>
       </c>
       <c r="R27" t="n">
-        <v>7299742</v>
+        <v>7299712</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3331,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400075</v>
+        <v>120400100</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3343,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777572</v>
+        <v>777528</v>
       </c>
       <c r="R28" t="n">
-        <v>7299804</v>
+        <v>7299721</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,6 +3415,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400089</v>
+        <v>120400079</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777544</v>
+        <v>777510</v>
       </c>
       <c r="R29" t="n">
-        <v>7299841</v>
+        <v>7299803</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400085</v>
+        <v>120400089</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,25 +3548,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777542</v>
+        <v>777544</v>
       </c>
       <c r="R30" t="n">
-        <v>7299749</v>
+        <v>7299841</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120400074</v>
+        <v>120400077</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777555</v>
+        <v>777488</v>
       </c>
       <c r="R31" t="n">
-        <v>7299761</v>
+        <v>7299834</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120400083</v>
+        <v>120400085</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777513</v>
+        <v>777542</v>
       </c>
       <c r="R32" t="n">
-        <v>7299751</v>
+        <v>7299749</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120400079</v>
+        <v>120400084</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -3885,7 +3885,7 @@
         <v>777510</v>
       </c>
       <c r="R33" t="n">
-        <v>7299803</v>
+        <v>7299742</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120400090</v>
+        <v>120400088</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777515</v>
+        <v>777536</v>
       </c>
       <c r="R34" t="n">
-        <v>7299848</v>
+        <v>7299724</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120400082</v>
+        <v>120400080</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777520</v>
+        <v>777509</v>
       </c>
       <c r="R35" t="n">
-        <v>7299766</v>
+        <v>7299785</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400077</v>
+        <v>120400086</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777488</v>
+        <v>777544</v>
       </c>
       <c r="R36" t="n">
-        <v>7299834</v>
+        <v>7299734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120400067</v>
+        <v>120400092</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777506</v>
+        <v>777528</v>
       </c>
       <c r="R37" t="n">
-        <v>7299869</v>
+        <v>7299779</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400095</v>
+        <v>120400076</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4364,25 +4364,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777538</v>
+        <v>777566</v>
       </c>
       <c r="R38" t="n">
-        <v>7299701</v>
+        <v>7299811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120447945</v>
+        <v>120447942</v>
       </c>
       <c r="B39" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4470,21 +4470,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777657</v>
+        <v>777618</v>
       </c>
       <c r="R39" t="n">
-        <v>7299864</v>
+        <v>7299777</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120447934</v>
+        <v>120447940</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4568,25 +4568,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777607</v>
+        <v>777720</v>
       </c>
       <c r="R40" t="n">
-        <v>7299771</v>
+        <v>7299943</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120447942</v>
+        <v>120447930</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777618</v>
+        <v>777677</v>
       </c>
       <c r="R41" t="n">
-        <v>7299777</v>
+        <v>7299863</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120447916</v>
+        <v>120447946</v>
       </c>
       <c r="B42" t="n">
-        <v>90084</v>
+        <v>82321</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4772,25 +4772,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>256703</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777801</v>
+        <v>777590</v>
       </c>
       <c r="R42" t="n">
-        <v>7299907</v>
+        <v>7299753</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120447930</v>
+        <v>120447943</v>
       </c>
       <c r="B43" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4874,25 +4874,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777677</v>
+        <v>777591</v>
       </c>
       <c r="R43" t="n">
-        <v>7299863</v>
+        <v>7299752</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120447923</v>
+        <v>120447917</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4976,25 +4976,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777708</v>
+        <v>777575</v>
       </c>
       <c r="R44" t="n">
-        <v>7299768</v>
+        <v>7299735</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120447926</v>
+        <v>120447927</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777821</v>
+        <v>777807</v>
       </c>
       <c r="R45" t="n">
-        <v>7299833</v>
+        <v>7299862</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120447946</v>
+        <v>120447933</v>
       </c>
       <c r="B46" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5180,25 +5180,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777590</v>
+        <v>777676</v>
       </c>
       <c r="R46" t="n">
-        <v>7299753</v>
+        <v>7299816</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120447914</v>
+        <v>120447924</v>
       </c>
       <c r="B47" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5282,25 +5282,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777574</v>
+        <v>777757</v>
       </c>
       <c r="R47" t="n">
-        <v>7299687</v>
+        <v>7299786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120447927</v>
+        <v>120447932</v>
       </c>
       <c r="B49" t="n">
         <v>97930</v>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777807</v>
+        <v>777654</v>
       </c>
       <c r="R49" t="n">
-        <v>7299862</v>
+        <v>7299823</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120447947</v>
+        <v>120447916</v>
       </c>
       <c r="B50" t="n">
-        <v>77926</v>
+        <v>90084</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5588,25 +5588,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6437</v>
+        <v>256703</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>777767</v>
+        <v>777801</v>
       </c>
       <c r="R50" t="n">
-        <v>7299946</v>
+        <v>7299907</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120447931</v>
+        <v>120447947</v>
       </c>
       <c r="B51" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5690,25 +5690,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>777660</v>
+        <v>777767</v>
       </c>
       <c r="R51" t="n">
-        <v>7299834</v>
+        <v>7299946</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120447932</v>
+        <v>120447931</v>
       </c>
       <c r="B52" t="n">
         <v>97930</v>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777654</v>
+        <v>777660</v>
       </c>
       <c r="R52" t="n">
-        <v>7299823</v>
+        <v>7299834</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120447915</v>
+        <v>120447926</v>
       </c>
       <c r="B53" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5894,25 +5894,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777762</v>
+        <v>777821</v>
       </c>
       <c r="R53" t="n">
-        <v>7299968</v>
+        <v>7299833</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,7 +5984,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120447935</v>
+        <v>120447934</v>
       </c>
       <c r="B54" t="n">
         <v>97930</v>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>777588</v>
+        <v>777607</v>
       </c>
       <c r="R54" t="n">
-        <v>7299750</v>
+        <v>7299771</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120447924</v>
+        <v>120447937</v>
       </c>
       <c r="B55" t="n">
         <v>97930</v>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>777757</v>
+        <v>777569</v>
       </c>
       <c r="R55" t="n">
-        <v>7299786</v>
+        <v>7299706</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120447928</v>
+        <v>120447945</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6200,25 +6200,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>777734</v>
+        <v>777657</v>
       </c>
       <c r="R56" t="n">
-        <v>7299914</v>
+        <v>7299864</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120447929</v>
+        <v>120447914</v>
       </c>
       <c r="B57" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6302,25 +6302,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>777717</v>
+        <v>777574</v>
       </c>
       <c r="R57" t="n">
-        <v>7299901</v>
+        <v>7299687</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6392,10 +6392,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120447943</v>
+        <v>120447928</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6404,25 +6404,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>777591</v>
+        <v>777734</v>
       </c>
       <c r="R58" t="n">
-        <v>7299752</v>
+        <v>7299914</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6494,7 +6494,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120447936</v>
+        <v>120447929</v>
       </c>
       <c r="B59" t="n">
         <v>97930</v>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>777575</v>
+        <v>777717</v>
       </c>
       <c r="R59" t="n">
-        <v>7299706</v>
+        <v>7299901</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120447937</v>
+        <v>120447923</v>
       </c>
       <c r="B60" t="n">
         <v>97930</v>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>777569</v>
+        <v>777708</v>
       </c>
       <c r="R60" t="n">
-        <v>7299706</v>
+        <v>7299768</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120447940</v>
+        <v>120447936</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6710,25 +6710,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>777720</v>
+        <v>777575</v>
       </c>
       <c r="R61" t="n">
-        <v>7299943</v>
+        <v>7299706</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6800,10 +6800,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120447933</v>
+        <v>120447915</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6812,25 +6812,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>777676</v>
+        <v>777762</v>
       </c>
       <c r="R62" t="n">
-        <v>7299816</v>
+        <v>7299968</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120447917</v>
+        <v>120447935</v>
       </c>
       <c r="B63" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777575</v>
+        <v>777588</v>
       </c>
       <c r="R63" t="n">
-        <v>7299735</v>
+        <v>7299750</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -3944,7 +3944,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120400088</v>
+        <v>120400080</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777536</v>
+        <v>777509</v>
       </c>
       <c r="R34" t="n">
-        <v>7299724</v>
+        <v>7299785</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120400080</v>
+        <v>120400088</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777509</v>
+        <v>777536</v>
       </c>
       <c r="R35" t="n">
-        <v>7299785</v>
+        <v>7299724</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120447945</v>
+        <v>120447914</v>
       </c>
       <c r="B56" t="n">
-        <v>82321</v>
+        <v>56532</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6200,25 +6200,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>777657</v>
+        <v>777574</v>
       </c>
       <c r="R56" t="n">
-        <v>7299864</v>
+        <v>7299687</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120447914</v>
+        <v>120447945</v>
       </c>
       <c r="B57" t="n">
-        <v>56532</v>
+        <v>82321</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6302,25 +6302,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>777574</v>
+        <v>777657</v>
       </c>
       <c r="R57" t="n">
-        <v>7299687</v>
+        <v>7299864</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276073</v>
+        <v>120276065</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777708</v>
+        <v>777859</v>
       </c>
       <c r="R2" t="n">
-        <v>7299857</v>
+        <v>7299767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,14 +770,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276068</v>
+        <v>120276070</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777581</v>
+        <v>777630</v>
       </c>
       <c r="R3" t="n">
-        <v>7299777</v>
+        <v>7299810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276070</v>
+        <v>120276069</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777630</v>
+        <v>777617</v>
       </c>
       <c r="R4" t="n">
-        <v>7299810</v>
+        <v>7299807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276071</v>
+        <v>120276076</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777669</v>
+        <v>777733</v>
       </c>
       <c r="R5" t="n">
-        <v>7299857</v>
+        <v>7299878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276069</v>
+        <v>120276071</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777617</v>
+        <v>777669</v>
       </c>
       <c r="R6" t="n">
-        <v>7299807</v>
+        <v>7299857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120276076</v>
+        <v>120276066</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777733</v>
+        <v>777536</v>
       </c>
       <c r="R7" t="n">
-        <v>7299878</v>
+        <v>7299705</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,14 +1284,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120276075</v>
+        <v>120276068</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777721</v>
+        <v>777581</v>
       </c>
       <c r="R8" t="n">
-        <v>7299859</v>
+        <v>7299777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120276065</v>
+        <v>120276072</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777859</v>
+        <v>777699</v>
       </c>
       <c r="R9" t="n">
-        <v>7299767</v>
+        <v>7299851</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,14 +1488,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120276072</v>
+        <v>120276073</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1531,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777699</v>
+        <v>777708</v>
       </c>
       <c r="R10" t="n">
-        <v>7299851</v>
+        <v>7299857</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120276066</v>
+        <v>120276075</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,42 +1609,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777536</v>
+        <v>777721</v>
       </c>
       <c r="R11" t="n">
-        <v>7299705</v>
+        <v>7299859</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,17 +1692,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120400066</v>
+        <v>120400080</v>
       </c>
       <c r="B12" t="n">
-        <v>90742</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,25 +1711,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777519</v>
+        <v>777509</v>
       </c>
       <c r="R12" t="n">
-        <v>7299799</v>
+        <v>7299785</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400083</v>
+        <v>120400097</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,25 +1813,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777513</v>
+        <v>777509</v>
       </c>
       <c r="R13" t="n">
-        <v>7299751</v>
+        <v>7299783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400090</v>
+        <v>120400084</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777515</v>
+        <v>777510</v>
       </c>
       <c r="R14" t="n">
-        <v>7299848</v>
+        <v>7299742</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120400067</v>
+        <v>120400075</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,25 +2017,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777506</v>
+        <v>777572</v>
       </c>
       <c r="R15" t="n">
-        <v>7299869</v>
+        <v>7299804</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120400068</v>
+        <v>120400083</v>
       </c>
       <c r="B16" t="n">
-        <v>77926</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777515</v>
+        <v>777513</v>
       </c>
       <c r="R16" t="n">
-        <v>7299746</v>
+        <v>7299751</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400073</v>
+        <v>120400100</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,25 +2221,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777546</v>
+        <v>777528</v>
       </c>
       <c r="R17" t="n">
-        <v>7299709</v>
+        <v>7299721</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2293,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2311,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120400075</v>
+        <v>120400090</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777572</v>
+        <v>777515</v>
       </c>
       <c r="R18" t="n">
-        <v>7299804</v>
+        <v>7299848</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,7 +2414,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400074</v>
+        <v>120400079</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2453,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777555</v>
+        <v>777510</v>
       </c>
       <c r="R19" t="n">
-        <v>7299761</v>
+        <v>7299803</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120400097</v>
+        <v>120400078</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777509</v>
+        <v>777481</v>
       </c>
       <c r="R20" t="n">
-        <v>7299783</v>
+        <v>7299820</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120400096</v>
+        <v>120400076</v>
       </c>
       <c r="B21" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777470</v>
+        <v>777566</v>
       </c>
       <c r="R21" t="n">
-        <v>7299820</v>
+        <v>7299811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120400078</v>
+        <v>120400096</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,7 +2760,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777481</v>
+        <v>777470</v>
       </c>
       <c r="R22" t="n">
         <v>7299820</v>
@@ -2821,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120400098</v>
+        <v>120400092</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2837,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2861,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777548</v>
+        <v>777528</v>
       </c>
       <c r="R23" t="n">
-        <v>7299735</v>
+        <v>7299779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120400081</v>
+        <v>120400068</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777538</v>
+        <v>777515</v>
       </c>
       <c r="R24" t="n">
-        <v>7299782</v>
+        <v>7299746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400082</v>
+        <v>120400086</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3065,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777520</v>
+        <v>777544</v>
       </c>
       <c r="R25" t="n">
-        <v>7299766</v>
+        <v>7299734</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120400095</v>
+        <v>120400085</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3167,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777538</v>
+        <v>777542</v>
       </c>
       <c r="R26" t="n">
-        <v>7299701</v>
+        <v>7299749</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120400094</v>
+        <v>120400073</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3269,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777533</v>
+        <v>777546</v>
       </c>
       <c r="R27" t="n">
-        <v>7299712</v>
+        <v>7299709</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3331,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400100</v>
+        <v>120400066</v>
       </c>
       <c r="B28" t="n">
-        <v>82321</v>
+        <v>90742</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3347,21 +3348,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3371,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777528</v>
+        <v>777519</v>
       </c>
       <c r="R28" t="n">
-        <v>7299721</v>
+        <v>7299799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3415,7 +3416,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400079</v>
+        <v>120400094</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777510</v>
+        <v>777533</v>
       </c>
       <c r="R29" t="n">
-        <v>7299803</v>
+        <v>7299712</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400089</v>
+        <v>120400081</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,25 +3548,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777544</v>
+        <v>777538</v>
       </c>
       <c r="R30" t="n">
-        <v>7299841</v>
+        <v>7299782</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120400085</v>
+        <v>120400074</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777542</v>
+        <v>777555</v>
       </c>
       <c r="R32" t="n">
-        <v>7299749</v>
+        <v>7299761</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120400084</v>
+        <v>120400089</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777510</v>
+        <v>777544</v>
       </c>
       <c r="R33" t="n">
-        <v>7299742</v>
+        <v>7299841</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120400080</v>
+        <v>120400067</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777509</v>
+        <v>777506</v>
       </c>
       <c r="R34" t="n">
-        <v>7299785</v>
+        <v>7299869</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120400088</v>
+        <v>120400098</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777536</v>
+        <v>777548</v>
       </c>
       <c r="R35" t="n">
-        <v>7299724</v>
+        <v>7299735</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400086</v>
+        <v>120400095</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777544</v>
+        <v>777538</v>
       </c>
       <c r="R36" t="n">
-        <v>7299734</v>
+        <v>7299701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120400092</v>
+        <v>120400088</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4262,25 +4262,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777528</v>
+        <v>777536</v>
       </c>
       <c r="R37" t="n">
-        <v>7299779</v>
+        <v>7299724</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400076</v>
+        <v>120400082</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777566</v>
+        <v>777520</v>
       </c>
       <c r="R38" t="n">
-        <v>7299811</v>
+        <v>7299766</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120447942</v>
+        <v>120447935</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4466,25 +4466,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777618</v>
+        <v>777588</v>
       </c>
       <c r="R39" t="n">
-        <v>7299777</v>
+        <v>7299750</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120447940</v>
+        <v>120447930</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4568,25 +4568,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777720</v>
+        <v>777677</v>
       </c>
       <c r="R40" t="n">
-        <v>7299943</v>
+        <v>7299863</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120447930</v>
+        <v>120447947</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777677</v>
+        <v>777767</v>
       </c>
       <c r="R41" t="n">
-        <v>7299863</v>
+        <v>7299946</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120447946</v>
+        <v>120447941</v>
       </c>
       <c r="B42" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777590</v>
+        <v>777712</v>
       </c>
       <c r="R42" t="n">
-        <v>7299753</v>
+        <v>7299892</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120447943</v>
+        <v>120447916</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>90084</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4874,25 +4874,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777591</v>
+        <v>777801</v>
       </c>
       <c r="R43" t="n">
-        <v>7299752</v>
+        <v>7299907</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120447917</v>
+        <v>120447926</v>
       </c>
       <c r="B44" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4976,25 +4976,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777575</v>
+        <v>777821</v>
       </c>
       <c r="R44" t="n">
-        <v>7299735</v>
+        <v>7299833</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120447927</v>
+        <v>120447914</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5078,25 +5078,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777807</v>
+        <v>777574</v>
       </c>
       <c r="R45" t="n">
-        <v>7299862</v>
+        <v>7299687</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5168,7 +5168,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120447933</v>
+        <v>120447937</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777676</v>
+        <v>777569</v>
       </c>
       <c r="R46" t="n">
-        <v>7299816</v>
+        <v>7299706</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5270,7 +5270,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120447924</v>
+        <v>120447934</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777757</v>
+        <v>777607</v>
       </c>
       <c r="R47" t="n">
-        <v>7299786</v>
+        <v>7299771</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5372,10 +5372,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120447941</v>
+        <v>120447917</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5384,25 +5384,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777712</v>
+        <v>777575</v>
       </c>
       <c r="R48" t="n">
-        <v>7299892</v>
+        <v>7299735</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5474,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120447932</v>
+        <v>120447915</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5486,25 +5486,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777654</v>
+        <v>777762</v>
       </c>
       <c r="R49" t="n">
-        <v>7299823</v>
+        <v>7299968</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120447916</v>
+        <v>120447946</v>
       </c>
       <c r="B50" t="n">
-        <v>90084</v>
+        <v>82321</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5588,25 +5588,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>256703</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>777801</v>
+        <v>777590</v>
       </c>
       <c r="R50" t="n">
-        <v>7299907</v>
+        <v>7299753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120447947</v>
+        <v>120447931</v>
       </c>
       <c r="B51" t="n">
-        <v>77926</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5690,25 +5690,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>777767</v>
+        <v>777660</v>
       </c>
       <c r="R51" t="n">
-        <v>7299946</v>
+        <v>7299834</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120447931</v>
+        <v>120447940</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5792,25 +5792,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777660</v>
+        <v>777720</v>
       </c>
       <c r="R52" t="n">
-        <v>7299834</v>
+        <v>7299943</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5882,7 +5882,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120447926</v>
+        <v>120447928</v>
       </c>
       <c r="B53" t="n">
         <v>97930</v>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777821</v>
+        <v>777734</v>
       </c>
       <c r="R53" t="n">
-        <v>7299833</v>
+        <v>7299914</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,7 +5984,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120447934</v>
+        <v>120447929</v>
       </c>
       <c r="B54" t="n">
         <v>97930</v>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>777607</v>
+        <v>777717</v>
       </c>
       <c r="R54" t="n">
-        <v>7299771</v>
+        <v>7299901</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120447937</v>
+        <v>120447932</v>
       </c>
       <c r="B55" t="n">
         <v>97930</v>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>777569</v>
+        <v>777654</v>
       </c>
       <c r="R55" t="n">
-        <v>7299706</v>
+        <v>7299823</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120447914</v>
+        <v>120447933</v>
       </c>
       <c r="B56" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6200,25 +6200,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>777574</v>
+        <v>777676</v>
       </c>
       <c r="R56" t="n">
-        <v>7299687</v>
+        <v>7299816</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120447945</v>
+        <v>120447943</v>
       </c>
       <c r="B57" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6306,21 +6306,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>777657</v>
+        <v>777591</v>
       </c>
       <c r="R57" t="n">
-        <v>7299864</v>
+        <v>7299752</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6392,7 +6392,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120447928</v>
+        <v>120447936</v>
       </c>
       <c r="B58" t="n">
         <v>97930</v>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>777734</v>
+        <v>777575</v>
       </c>
       <c r="R58" t="n">
-        <v>7299914</v>
+        <v>7299706</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120447929</v>
+        <v>120447942</v>
       </c>
       <c r="B59" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6506,25 +6506,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>777717</v>
+        <v>777618</v>
       </c>
       <c r="R59" t="n">
-        <v>7299901</v>
+        <v>7299777</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120447923</v>
+        <v>120447924</v>
       </c>
       <c r="B60" t="n">
         <v>97930</v>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>777708</v>
+        <v>777757</v>
       </c>
       <c r="R60" t="n">
-        <v>7299768</v>
+        <v>7299786</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120447936</v>
+        <v>120447945</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6710,25 +6710,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>777575</v>
+        <v>777657</v>
       </c>
       <c r="R61" t="n">
-        <v>7299706</v>
+        <v>7299864</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6800,10 +6800,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120447915</v>
+        <v>120447927</v>
       </c>
       <c r="B62" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6812,25 +6812,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>777762</v>
+        <v>777807</v>
       </c>
       <c r="R62" t="n">
-        <v>7299968</v>
+        <v>7299862</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6902,7 +6902,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120447935</v>
+        <v>120447923</v>
       </c>
       <c r="B63" t="n">
         <v>97930</v>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777588</v>
+        <v>777708</v>
       </c>
       <c r="R63" t="n">
-        <v>7299750</v>
+        <v>7299768</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276065</v>
+        <v>120276069</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777859</v>
+        <v>777617</v>
       </c>
       <c r="R2" t="n">
-        <v>7299767</v>
+        <v>7299807</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,14 +770,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276070</v>
+        <v>120276068</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777630</v>
+        <v>777581</v>
       </c>
       <c r="R3" t="n">
-        <v>7299810</v>
+        <v>7299777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276069</v>
+        <v>120276065</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777617</v>
+        <v>777859</v>
       </c>
       <c r="R4" t="n">
-        <v>7299807</v>
+        <v>7299767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,14 +974,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276076</v>
+        <v>120276072</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777733</v>
+        <v>777699</v>
       </c>
       <c r="R5" t="n">
-        <v>7299878</v>
+        <v>7299851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120276068</v>
+        <v>120276075</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777581</v>
+        <v>777721</v>
       </c>
       <c r="R8" t="n">
-        <v>7299777</v>
+        <v>7299859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120276072</v>
+        <v>120276076</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777699</v>
+        <v>777733</v>
       </c>
       <c r="R9" t="n">
-        <v>7299851</v>
+        <v>7299878</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120276075</v>
+        <v>120276070</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777721</v>
+        <v>777630</v>
       </c>
       <c r="R11" t="n">
-        <v>7299859</v>
+        <v>7299810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120400080</v>
+        <v>120400095</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,25 +1711,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777509</v>
+        <v>777538</v>
       </c>
       <c r="R12" t="n">
-        <v>7299785</v>
+        <v>7299701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400097</v>
+        <v>120400079</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,25 +1813,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777509</v>
+        <v>777510</v>
       </c>
       <c r="R13" t="n">
-        <v>7299783</v>
+        <v>7299803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400084</v>
+        <v>120400085</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777510</v>
+        <v>777542</v>
       </c>
       <c r="R14" t="n">
-        <v>7299742</v>
+        <v>7299749</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120400075</v>
+        <v>120400068</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,25 +2017,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777572</v>
+        <v>777515</v>
       </c>
       <c r="R15" t="n">
-        <v>7299804</v>
+        <v>7299746</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120400083</v>
+        <v>120400097</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777513</v>
+        <v>777509</v>
       </c>
       <c r="R16" t="n">
-        <v>7299751</v>
+        <v>7299783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400100</v>
+        <v>120400094</v>
       </c>
       <c r="B17" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2225,21 +2225,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777528</v>
+        <v>777533</v>
       </c>
       <c r="R17" t="n">
-        <v>7299721</v>
+        <v>7299712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,7 +2293,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2312,10 +2311,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120400090</v>
+        <v>120400074</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2323,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777515</v>
+        <v>777555</v>
       </c>
       <c r="R18" t="n">
-        <v>7299848</v>
+        <v>7299761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,7 +2413,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400079</v>
+        <v>120400086</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2454,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777510</v>
+        <v>777544</v>
       </c>
       <c r="R19" t="n">
-        <v>7299803</v>
+        <v>7299734</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,7 +2515,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120400078</v>
+        <v>120400084</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2556,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777481</v>
+        <v>777510</v>
       </c>
       <c r="R20" t="n">
-        <v>7299820</v>
+        <v>7299742</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120400096</v>
+        <v>120400080</v>
       </c>
       <c r="B22" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2731,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777470</v>
+        <v>777509</v>
       </c>
       <c r="R22" t="n">
-        <v>7299820</v>
+        <v>7299785</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120400092</v>
+        <v>120400075</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2833,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777528</v>
+        <v>777572</v>
       </c>
       <c r="R23" t="n">
-        <v>7299779</v>
+        <v>7299804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120400068</v>
+        <v>120400096</v>
       </c>
       <c r="B24" t="n">
-        <v>77926</v>
+        <v>82321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2939,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777515</v>
+        <v>777470</v>
       </c>
       <c r="R24" t="n">
-        <v>7299746</v>
+        <v>7299820</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3025,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400086</v>
+        <v>120400067</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3037,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777544</v>
+        <v>777506</v>
       </c>
       <c r="R25" t="n">
-        <v>7299734</v>
+        <v>7299869</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3127,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120400085</v>
+        <v>120400100</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3139,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777542</v>
+        <v>777528</v>
       </c>
       <c r="R26" t="n">
-        <v>7299749</v>
+        <v>7299721</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,6 +3211,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120400073</v>
+        <v>120400092</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777546</v>
+        <v>777528</v>
       </c>
       <c r="R27" t="n">
-        <v>7299709</v>
+        <v>7299779</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400066</v>
+        <v>120400089</v>
       </c>
       <c r="B28" t="n">
-        <v>90742</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777519</v>
+        <v>777544</v>
       </c>
       <c r="R28" t="n">
-        <v>7299799</v>
+        <v>7299841</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400094</v>
+        <v>120400081</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777533</v>
+        <v>777538</v>
       </c>
       <c r="R29" t="n">
-        <v>7299712</v>
+        <v>7299782</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400081</v>
+        <v>120400083</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777538</v>
+        <v>777513</v>
       </c>
       <c r="R30" t="n">
-        <v>7299782</v>
+        <v>7299751</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120400077</v>
+        <v>120400082</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777488</v>
+        <v>777520</v>
       </c>
       <c r="R31" t="n">
-        <v>7299834</v>
+        <v>7299766</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120400074</v>
+        <v>120400088</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777555</v>
+        <v>777536</v>
       </c>
       <c r="R32" t="n">
-        <v>7299761</v>
+        <v>7299724</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120400089</v>
+        <v>120400066</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>90742</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777544</v>
+        <v>777519</v>
       </c>
       <c r="R33" t="n">
-        <v>7299841</v>
+        <v>7299799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120400067</v>
+        <v>120400077</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777506</v>
+        <v>777488</v>
       </c>
       <c r="R34" t="n">
-        <v>7299869</v>
+        <v>7299834</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120400098</v>
+        <v>120400090</v>
       </c>
       <c r="B35" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777548</v>
+        <v>777515</v>
       </c>
       <c r="R35" t="n">
-        <v>7299735</v>
+        <v>7299848</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400095</v>
+        <v>120400073</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777538</v>
+        <v>777546</v>
       </c>
       <c r="R36" t="n">
-        <v>7299701</v>
+        <v>7299709</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120400088</v>
+        <v>120400078</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777536</v>
+        <v>777481</v>
       </c>
       <c r="R37" t="n">
-        <v>7299724</v>
+        <v>7299820</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400082</v>
+        <v>120400098</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4364,25 +4364,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777520</v>
+        <v>777548</v>
       </c>
       <c r="R38" t="n">
-        <v>7299766</v>
+        <v>7299735</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120447935</v>
+        <v>120447947</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4466,25 +4466,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777588</v>
+        <v>777767</v>
       </c>
       <c r="R39" t="n">
-        <v>7299750</v>
+        <v>7299946</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120447930</v>
+        <v>120447929</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777677</v>
+        <v>777717</v>
       </c>
       <c r="R40" t="n">
-        <v>7299863</v>
+        <v>7299901</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120447947</v>
+        <v>120447924</v>
       </c>
       <c r="B41" t="n">
-        <v>77926</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777767</v>
+        <v>777757</v>
       </c>
       <c r="R41" t="n">
-        <v>7299946</v>
+        <v>7299786</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120447941</v>
+        <v>120447915</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777712</v>
+        <v>777762</v>
       </c>
       <c r="R42" t="n">
-        <v>7299892</v>
+        <v>7299968</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120447916</v>
+        <v>120447942</v>
       </c>
       <c r="B43" t="n">
-        <v>90084</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4874,25 +4874,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777801</v>
+        <v>777618</v>
       </c>
       <c r="R43" t="n">
-        <v>7299907</v>
+        <v>7299777</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120447926</v>
+        <v>120447927</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777821</v>
+        <v>777807</v>
       </c>
       <c r="R44" t="n">
-        <v>7299833</v>
+        <v>7299862</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120447914</v>
+        <v>120447931</v>
       </c>
       <c r="B45" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5078,25 +5078,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777574</v>
+        <v>777660</v>
       </c>
       <c r="R45" t="n">
-        <v>7299687</v>
+        <v>7299834</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5168,7 +5168,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120447937</v>
+        <v>120447923</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777569</v>
+        <v>777708</v>
       </c>
       <c r="R46" t="n">
-        <v>7299706</v>
+        <v>7299768</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5372,10 +5372,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120447917</v>
+        <v>120447941</v>
       </c>
       <c r="B48" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5384,25 +5384,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777575</v>
+        <v>777712</v>
       </c>
       <c r="R48" t="n">
-        <v>7299735</v>
+        <v>7299892</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5474,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120447915</v>
+        <v>120447917</v>
       </c>
       <c r="B49" t="n">
-        <v>57473</v>
+        <v>79652</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5486,25 +5486,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777762</v>
+        <v>777575</v>
       </c>
       <c r="R49" t="n">
-        <v>7299968</v>
+        <v>7299735</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120447946</v>
+        <v>120447932</v>
       </c>
       <c r="B50" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5588,25 +5588,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>777590</v>
+        <v>777654</v>
       </c>
       <c r="R50" t="n">
-        <v>7299753</v>
+        <v>7299823</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120447931</v>
+        <v>120447930</v>
       </c>
       <c r="B51" t="n">
         <v>97930</v>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>777660</v>
+        <v>777677</v>
       </c>
       <c r="R51" t="n">
-        <v>7299834</v>
+        <v>7299863</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120447940</v>
+        <v>120447914</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5792,25 +5792,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777720</v>
+        <v>777574</v>
       </c>
       <c r="R52" t="n">
-        <v>7299943</v>
+        <v>7299687</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5882,7 +5882,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120447928</v>
+        <v>120447933</v>
       </c>
       <c r="B53" t="n">
         <v>97930</v>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777734</v>
+        <v>777676</v>
       </c>
       <c r="R53" t="n">
-        <v>7299914</v>
+        <v>7299816</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,10 +5984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120447929</v>
+        <v>120447946</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5996,25 +5996,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>777717</v>
+        <v>777590</v>
       </c>
       <c r="R54" t="n">
-        <v>7299901</v>
+        <v>7299753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6086,10 +6086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120447932</v>
+        <v>120447916</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>90084</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6098,25 +6098,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>777654</v>
+        <v>777801</v>
       </c>
       <c r="R55" t="n">
-        <v>7299823</v>
+        <v>7299907</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6188,7 +6188,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120447933</v>
+        <v>120447936</v>
       </c>
       <c r="B56" t="n">
         <v>97930</v>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>777676</v>
+        <v>777575</v>
       </c>
       <c r="R56" t="n">
-        <v>7299816</v>
+        <v>7299706</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120447943</v>
+        <v>120447935</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6302,25 +6302,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>777591</v>
+        <v>777588</v>
       </c>
       <c r="R57" t="n">
-        <v>7299752</v>
+        <v>7299750</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6392,10 +6392,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120447936</v>
+        <v>120447943</v>
       </c>
       <c r="B58" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6404,25 +6404,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>777575</v>
+        <v>777591</v>
       </c>
       <c r="R58" t="n">
-        <v>7299706</v>
+        <v>7299752</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120447942</v>
+        <v>120447926</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6506,25 +6506,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>777618</v>
+        <v>777821</v>
       </c>
       <c r="R59" t="n">
-        <v>7299777</v>
+        <v>7299833</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120447924</v>
+        <v>120447928</v>
       </c>
       <c r="B60" t="n">
         <v>97930</v>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>777757</v>
+        <v>777734</v>
       </c>
       <c r="R60" t="n">
-        <v>7299786</v>
+        <v>7299914</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120447945</v>
+        <v>120447937</v>
       </c>
       <c r="B61" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6710,25 +6710,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>777657</v>
+        <v>777569</v>
       </c>
       <c r="R61" t="n">
-        <v>7299864</v>
+        <v>7299706</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6800,10 +6800,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120447927</v>
+        <v>120447945</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6812,25 +6812,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>777807</v>
+        <v>777657</v>
       </c>
       <c r="R62" t="n">
-        <v>7299862</v>
+        <v>7299864</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120447923</v>
+        <v>120447940</v>
       </c>
       <c r="B63" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777708</v>
+        <v>777720</v>
       </c>
       <c r="R63" t="n">
-        <v>7299768</v>
+        <v>7299943</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -4250,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120400078</v>
+        <v>120400098</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4262,25 +4262,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777481</v>
+        <v>777548</v>
       </c>
       <c r="R37" t="n">
-        <v>7299820</v>
+        <v>7299735</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400098</v>
+        <v>120400078</v>
       </c>
       <c r="B38" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4364,25 +4364,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777548</v>
+        <v>777481</v>
       </c>
       <c r="R38" t="n">
-        <v>7299735</v>
+        <v>7299820</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120447947</v>
+        <v>120447929</v>
       </c>
       <c r="B39" t="n">
-        <v>77926</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4466,25 +4466,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777767</v>
+        <v>777717</v>
       </c>
       <c r="R39" t="n">
-        <v>7299946</v>
+        <v>7299901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120447929</v>
+        <v>120447924</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777717</v>
+        <v>777757</v>
       </c>
       <c r="R40" t="n">
-        <v>7299901</v>
+        <v>7299786</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120447924</v>
+        <v>120447947</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777757</v>
+        <v>777767</v>
       </c>
       <c r="R41" t="n">
-        <v>7299786</v>
+        <v>7299946</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120447915</v>
+        <v>120447942</v>
       </c>
       <c r="B42" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777762</v>
+        <v>777618</v>
       </c>
       <c r="R42" t="n">
-        <v>7299968</v>
+        <v>7299777</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120447942</v>
+        <v>120447915</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777618</v>
+        <v>777762</v>
       </c>
       <c r="R43" t="n">
-        <v>7299777</v>
+        <v>7299968</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5168,7 +5168,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120447923</v>
+        <v>120447934</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777708</v>
+        <v>777607</v>
       </c>
       <c r="R46" t="n">
-        <v>7299768</v>
+        <v>7299771</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5270,7 +5270,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120447934</v>
+        <v>120447923</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777607</v>
+        <v>777708</v>
       </c>
       <c r="R47" t="n">
-        <v>7299771</v>
+        <v>7299768</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5984,10 +5984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120447946</v>
+        <v>120447916</v>
       </c>
       <c r="B54" t="n">
-        <v>82321</v>
+        <v>90084</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5996,25 +5996,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>256703</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>777590</v>
+        <v>777801</v>
       </c>
       <c r="R54" t="n">
-        <v>7299753</v>
+        <v>7299907</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6086,10 +6086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120447916</v>
+        <v>120447946</v>
       </c>
       <c r="B55" t="n">
-        <v>90084</v>
+        <v>82321</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6098,25 +6098,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>256703</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>777801</v>
+        <v>777590</v>
       </c>
       <c r="R55" t="n">
-        <v>7299907</v>
+        <v>7299753</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -5681,11 +5681,11 @@
         <v>120447914</v>
       </c>
       <c r="B51" t="n">
-        <v>56556</v>
+        <v>56593</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -5681,7 +5681,7 @@
         <v>120447914</v>
       </c>
       <c r="B51" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6900,6 +6900,312 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122857763</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>777546</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7299744</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122857764</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>777678</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7299871</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122857766</v>
+      </c>
+      <c r="B65" t="n">
+        <v>95648</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>777625</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7299819</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6902,7 +6902,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122857763</v>
+        <v>122857764</v>
       </c>
       <c r="B63" t="n">
         <v>98355</v>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777546</v>
+        <v>777678</v>
       </c>
       <c r="R63" t="n">
-        <v>7299744</v>
+        <v>7299871</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122857764</v>
+        <v>122857766</v>
       </c>
       <c r="B64" t="n">
-        <v>98355</v>
+        <v>95648</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7016,25 +7016,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>777678</v>
+        <v>777625</v>
       </c>
       <c r="R64" t="n">
-        <v>7299871</v>
+        <v>7299819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857766</v>
+        <v>122857763</v>
       </c>
       <c r="B65" t="n">
-        <v>95648</v>
+        <v>98355</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777625</v>
+        <v>777546</v>
       </c>
       <c r="R65" t="n">
-        <v>7299819</v>
+        <v>7299744</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122857764</v>
+        <v>122857763</v>
       </c>
       <c r="B63" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777678</v>
+        <v>777546</v>
       </c>
       <c r="R63" t="n">
-        <v>7299871</v>
+        <v>7299744</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
         <v>122857766</v>
       </c>
       <c r="B64" t="n">
-        <v>95648</v>
+        <v>95650</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857763</v>
+        <v>122857764</v>
       </c>
       <c r="B65" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777546</v>
+        <v>777678</v>
       </c>
       <c r="R65" t="n">
-        <v>7299744</v>
+        <v>7299871</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6902,7 +6902,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122857763</v>
+        <v>122857764</v>
       </c>
       <c r="B63" t="n">
         <v>98357</v>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777546</v>
+        <v>777678</v>
       </c>
       <c r="R63" t="n">
-        <v>7299744</v>
+        <v>7299871</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122857766</v>
+        <v>122857763</v>
       </c>
       <c r="B64" t="n">
-        <v>95650</v>
+        <v>98357</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7016,25 +7016,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>777625</v>
+        <v>777546</v>
       </c>
       <c r="R64" t="n">
-        <v>7299819</v>
+        <v>7299744</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857764</v>
+        <v>122857766</v>
       </c>
       <c r="B65" t="n">
-        <v>98357</v>
+        <v>95650</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777678</v>
+        <v>777625</v>
       </c>
       <c r="R65" t="n">
-        <v>7299871</v>
+        <v>7299819</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6905,7 +6905,7 @@
         <v>122857764</v>
       </c>
       <c r="B63" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122857763</v>
+        <v>122857766</v>
       </c>
       <c r="B64" t="n">
-        <v>98357</v>
+        <v>95658</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7016,25 +7016,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>777546</v>
+        <v>777625</v>
       </c>
       <c r="R64" t="n">
-        <v>7299744</v>
+        <v>7299819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857766</v>
+        <v>122857763</v>
       </c>
       <c r="B65" t="n">
-        <v>95650</v>
+        <v>98365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777625</v>
+        <v>777546</v>
       </c>
       <c r="R65" t="n">
-        <v>7299819</v>
+        <v>7299744</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122857764</v>
+        <v>122857766</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>95658</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777678</v>
+        <v>777625</v>
       </c>
       <c r="R63" t="n">
-        <v>7299871</v>
+        <v>7299819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122857766</v>
+        <v>122857764</v>
       </c>
       <c r="B64" t="n">
-        <v>95658</v>
+        <v>98365</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7016,25 +7016,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>777625</v>
+        <v>777678</v>
       </c>
       <c r="R64" t="n">
-        <v>7299819</v>
+        <v>7299871</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122857766</v>
+        <v>122857764</v>
       </c>
       <c r="B63" t="n">
-        <v>95658</v>
+        <v>98365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777625</v>
+        <v>777678</v>
       </c>
       <c r="R63" t="n">
-        <v>7299819</v>
+        <v>7299871</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122857764</v>
+        <v>122857763</v>
       </c>
       <c r="B64" t="n">
         <v>98365</v>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>777678</v>
+        <v>777546</v>
       </c>
       <c r="R64" t="n">
-        <v>7299871</v>
+        <v>7299744</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857763</v>
+        <v>122857766</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>95658</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777546</v>
+        <v>777625</v>
       </c>
       <c r="R65" t="n">
-        <v>7299744</v>
+        <v>7299819</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -7004,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122857763</v>
+        <v>122857766</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>95658</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7016,25 +7016,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>777546</v>
+        <v>777625</v>
       </c>
       <c r="R64" t="n">
-        <v>7299744</v>
+        <v>7299819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857766</v>
+        <v>122857763</v>
       </c>
       <c r="B65" t="n">
-        <v>95658</v>
+        <v>98365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777625</v>
+        <v>777546</v>
       </c>
       <c r="R65" t="n">
-        <v>7299819</v>
+        <v>7299744</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122857764</v>
+        <v>122857766</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>95661</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777678</v>
+        <v>777625</v>
       </c>
       <c r="R63" t="n">
-        <v>7299871</v>
+        <v>7299819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122857766</v>
+        <v>122857763</v>
       </c>
       <c r="B64" t="n">
-        <v>95658</v>
+        <v>98368</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7016,25 +7016,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>777625</v>
+        <v>777546</v>
       </c>
       <c r="R64" t="n">
-        <v>7299819</v>
+        <v>7299744</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857763</v>
+        <v>122857764</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777546</v>
+        <v>777678</v>
       </c>
       <c r="R65" t="n">
-        <v>7299744</v>
+        <v>7299871</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122857766</v>
+        <v>122857764</v>
       </c>
       <c r="B63" t="n">
-        <v>95661</v>
+        <v>98370</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777625</v>
+        <v>777678</v>
       </c>
       <c r="R63" t="n">
-        <v>7299819</v>
+        <v>7299871</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
         <v>122857763</v>
       </c>
       <c r="B64" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857764</v>
+        <v>122857766</v>
       </c>
       <c r="B65" t="n">
-        <v>98368</v>
+        <v>95663</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777678</v>
+        <v>777625</v>
       </c>
       <c r="R65" t="n">
-        <v>7299871</v>
+        <v>7299819</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 40109-2024 artfynd.xlsx
+++ b/artfynd/A 40109-2024 artfynd.xlsx
@@ -6902,10 +6902,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122857764</v>
+        <v>122857766</v>
       </c>
       <c r="B63" t="n">
-        <v>98370</v>
+        <v>95669</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777678</v>
+        <v>777625</v>
       </c>
       <c r="R63" t="n">
-        <v>7299871</v>
+        <v>7299819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
         <v>122857763</v>
       </c>
       <c r="B64" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122857766</v>
+        <v>122857764</v>
       </c>
       <c r="B65" t="n">
-        <v>95663</v>
+        <v>98376</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777625</v>
+        <v>777678</v>
       </c>
       <c r="R65" t="n">
-        <v>7299819</v>
+        <v>7299871</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
